--- a/data/trending_integrated_20261019_12.xlsx
+++ b/data/trending_integrated_20261019_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20381066184</v>
+        <v>20413423412</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9460</v>
+        <v>9420</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.95%</t>
+          <t>'+11.48%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>21420770950</v>
+        <v>21979040740</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 수혜주로서의 명신산업 언급. 공매도 및 프로그램 매매 관련 내용 포함. 단기 상승 기대.</t>
+          <t>테슬라 로드스터 수혜주로서의 기대감이 언급되었으나, 공매도 및 매도세에 대한 우려도 존재. 자사주 매입 관련 언급이 있으며, 만원대 돌파 여부가 관건.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -747,162 +747,162 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171200</v>
+        <v>9310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+3.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="H4" t="n">
-        <v>75.02</v>
+        <v>1.74</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>167200</v>
+        <v>9010</v>
       </c>
       <c r="K4" t="n">
-        <v>159600</v>
+        <v>8810</v>
       </c>
       <c r="L4" t="n">
-        <v>175500</v>
+        <v>9500</v>
       </c>
       <c r="M4" t="n">
-        <v>159200</v>
+        <v>8510</v>
       </c>
       <c r="N4" t="n">
-        <v>75</v>
+        <v>0.72</v>
       </c>
       <c r="O4" t="n">
-        <v>421480940800</v>
+        <v>118820457510</v>
       </c>
       <c r="P4" t="n">
-        <v>243500</v>
+        <v>9500</v>
       </c>
       <c r="Q4" t="n">
-        <v>71000</v>
+        <v>2270</v>
       </c>
       <c r="R4" t="n">
-        <v>59000</v>
+        <v>-181000</v>
       </c>
       <c r="S4" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t>시장 전반의 불안감 속에서 로봇주에 대한 긍정적인 전망이 일부 있으나, 개인 투자자들의 혼란과 손실에 대한 우려가 혼재. 분석글 공개 후 급락 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['로봇주', '시장', '분석글']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9170</v>
+        <v>171200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.78%</t>
+          <t>'+2.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>96</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>75.02</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9010</v>
+        <v>167200</v>
       </c>
       <c r="K5" t="n">
-        <v>8810</v>
+        <v>159600</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>175500</v>
       </c>
       <c r="M5" t="n">
-        <v>8510</v>
+        <v>159200</v>
       </c>
       <c r="N5" t="n">
-        <v>0.72</v>
+        <v>75</v>
       </c>
       <c r="O5" t="n">
-        <v>113441806280</v>
+        <v>431282026800</v>
       </c>
       <c r="P5" t="n">
-        <v>9500</v>
+        <v>243500</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>71000</v>
       </c>
       <c r="R5" t="n">
-        <v>-181000</v>
+        <v>59000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>종목 토론방 내 단기적인 시장 상황 및 개인적인 매매 경험 공유. 특정 가격대 도달 기대감 있으나 구체적인 근거 제시 부족.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,51 +911,51 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇주', '매도', '장기조정']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>216500</v>
+        <v>14900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'+1.15%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
       <c r="F6" t="n">
-        <v>505</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>1450</v>
+        <v>169</v>
       </c>
       <c r="H6" t="n">
-        <v>45.99</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>215500</v>
+        <v>14730</v>
       </c>
       <c r="K6" t="n">
-        <v>207000</v>
+        <v>14500</v>
       </c>
       <c r="L6" t="n">
-        <v>219500</v>
+        <v>15070</v>
       </c>
       <c r="M6" t="n">
-        <v>206500</v>
+        <v>14120</v>
       </c>
       <c r="N6" t="n">
-        <v>45.98</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>1808607644750</v>
+        <v>24868303940</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>1715000</v>
+        <v>32000</v>
       </c>
       <c r="S6" t="n">
-        <v>573000</v>
+        <v>-29000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>이재명 관련 정치적 발언 및 개인적인 매매 경험 공유. 악재 소진 후 반등 기대감 존재하나 구체적인 근거 부족.</t>
+          <t>대우건설, 정치적 이슈와 연관된 부정적 언급 다수. 뱅크런 및 주가 조작 의혹 제기, 외인 보유율 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['이재명', '연기금', '매수']</t>
+          <t>['뱅크런', '주가조작', '이재명']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,191 +1016,191 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14990</v>
+        <v>217000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>34</v>
+        <v>506</v>
       </c>
       <c r="G7" t="n">
-        <v>69</v>
+        <v>1445</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06</v>
+        <v>45.99</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14950</v>
+        <v>215500</v>
       </c>
       <c r="K7" t="n">
-        <v>14610</v>
+        <v>207000</v>
       </c>
       <c r="L7" t="n">
-        <v>16600</v>
+        <v>219500</v>
       </c>
       <c r="M7" t="n">
-        <v>14610</v>
+        <v>206500</v>
       </c>
       <c r="N7" t="n">
-        <v>0.11</v>
+        <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>26109934110</v>
+        <v>1871957792250</v>
       </c>
       <c r="P7" t="n">
-        <v>30800</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>9810</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>23000</v>
+        <v>1715000</v>
       </c>
       <c r="S7" t="n">
-        <v>1000</v>
+        <v>573000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
+          <t>이재명, 연기금 관련 정치적 언급과 더불어 주가 등락에 대한 다양한 기대와 우려가 혼재된 상황. 공매도 및 기관 매매 동향에 대한 언급이 있으나, 구체적인 근거는 부족.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['하이드로겔', '주문폭증', '신규주']</t>
+          <t>['연기금', '공매도', '매매동향']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14770</v>
+        <v>14910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>167</v>
+        <v>71</v>
       </c>
       <c r="H8" t="n">
-        <v>9.699999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14730</v>
+        <v>14950</v>
       </c>
       <c r="K8" t="n">
-        <v>14500</v>
+        <v>14610</v>
       </c>
       <c r="L8" t="n">
-        <v>14910</v>
+        <v>16600</v>
       </c>
       <c r="M8" t="n">
-        <v>14120</v>
+        <v>14610</v>
       </c>
       <c r="N8" t="n">
-        <v>9.779999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>21983125295</v>
+        <v>26613768620</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>30800</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>9810</v>
       </c>
       <c r="R8" t="n">
-        <v>32000</v>
+        <v>23000</v>
       </c>
       <c r="S8" t="n">
-        <v>-29000</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 이슈와 연관된 부정적 언급 다수. 뱅크런 및 주가 조작 의혹 제기, 외인 보유율 관련 언급.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['뱅크런', '주가조작', '이재명']</t>
+          <t>['하이드로겔', '주문폭증', '신규주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1253000</v>
+        <v>1258000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.49%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="G9" t="n">
-        <v>1736</v>
+        <v>1796</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2387413741000</v>
+        <v>2492083719500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 관련 논란 및 최태원 회장에 대한 비판적 의견 다수. 주가 하락에 대한 부정적 전망.</t>
+          <t>솔리다임 상장 문제와 관련된 부정적인 의견이 지배적이며, 최태원 회장에 대한 비난과 경영 투명성 부족에 대한 지적이 다수. 안철수 의원의 발언이 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '최태원', '주주']</t>
+          <t>['솔리다임', '최태원', '상장']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17810</v>
+        <v>17850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-2.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>27482795255</v>
+        <v>28021727200</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1391,28 +1391,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1209</v>
+        <v>14390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.12%</t>
+          <t>'-4.13%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1261</v>
+        <v>15010</v>
       </c>
       <c r="K11" t="n">
-        <v>1301</v>
+        <v>14460</v>
       </c>
       <c r="L11" t="n">
-        <v>1339</v>
+        <v>15200</v>
       </c>
       <c r="M11" t="n">
-        <v>1145</v>
+        <v>13610</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>10507899240</v>
+        <v>36776921795</v>
       </c>
       <c r="P11" t="n">
-        <v>1950</v>
+        <v>28800</v>
       </c>
       <c r="Q11" t="n">
-        <v>192</v>
+        <v>13610</v>
       </c>
       <c r="R11" t="n">
-        <v>-321000</v>
+        <v>35000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
+          <t>멜콘, 과거 거래 이력 및 주포 활동 분석. 투자 주의 의견 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['데이터센터', 'AI', '성장성']</t>
+          <t>['주포', '거래량', '투자주의']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,35 +1476,35 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>317240</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14120</v>
+        <v>1194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.93%</t>
+          <t>'-5.31%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15010</v>
+        <v>1261</v>
       </c>
       <c r="K12" t="n">
-        <v>14460</v>
+        <v>1301</v>
       </c>
       <c r="L12" t="n">
-        <v>15200</v>
+        <v>1339</v>
       </c>
       <c r="M12" t="n">
-        <v>13610</v>
+        <v>1145</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>35643531725</v>
+        <v>10757366524</v>
       </c>
       <c r="P12" t="n">
-        <v>28800</v>
+        <v>1950</v>
       </c>
       <c r="Q12" t="n">
-        <v>13610</v>
+        <v>192</v>
       </c>
       <c r="R12" t="n">
-        <v>35000</v>
+        <v>-321000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>멜콘, 과거 거래 이력 및 주포 활동 분석. 투자 주의 의견 제기.</t>
+          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '투자주의']</t>
+          <t>['데이터센터', 'AI', '성장성']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>317240</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261019_12.xlsx
+++ b/data/trending_integrated_20261019_12.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.96%</t>
+          <t>'+38.84%</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -584,7 +584,7 @@
         <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1345</v>
+        <v>1259</v>
       </c>
       <c r="K2" t="n">
-        <v>1432</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1748</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1386</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20413423412</v>
+        <v>20424000000</v>
       </c>
       <c r="P2" t="n">
-        <v>2970</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>890</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>918000</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 관련 뉴스 확인. 외인 매수세 유입에 따른 주가 상승 기대감.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 소식에 대한 기대감 고조. 외인 매집 확인, 전고점 돌파 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9420</v>
+        <v>9470</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.48%</t>
+          <t>'+12.07%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>21979040740</v>
+        <v>22226445530</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 수혜주로서의 기대감이 언급되었으나, 공매도 및 매도세에 대한 우려도 존재. 자사주 매입 관련 언급이 있으며, 만원대 돌파 여부가 관건.</t>
+          <t>명신산업, 테슬라 로드스터 수혜주로 부각되며 전체 매출의 70% 테슬라 납품 사실에 주목. 11,000원 돌파 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '공매도']</t>
+          <t>['테슬라', '로드스터', '납품']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,184 +747,184 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9310</v>
+        <v>171000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+3.33%</t>
+          <t>'+2.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H4" t="n">
-        <v>1.74</v>
+        <v>75.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9010</v>
+        <v>167200</v>
       </c>
       <c r="K4" t="n">
-        <v>8810</v>
+        <v>159600</v>
       </c>
       <c r="L4" t="n">
-        <v>9500</v>
+        <v>175500</v>
       </c>
       <c r="M4" t="n">
-        <v>8510</v>
+        <v>159200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.72</v>
+        <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>118820457510</v>
+        <v>438544201850</v>
       </c>
       <c r="P4" t="n">
-        <v>9500</v>
+        <v>243500</v>
       </c>
       <c r="Q4" t="n">
-        <v>2270</v>
+        <v>71000</v>
       </c>
       <c r="R4" t="n">
-        <v>-181000</v>
+        <v>59000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>시장 전반의 불안감 속에서 로봇주에 대한 긍정적인 전망이 일부 있으나, 개인 투자자들의 혼란과 손실에 대한 우려가 혼재. 분석글 공개 후 급락 가능성에 대한 언급.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇주', '시장', '분석글']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>171200</v>
+        <v>9190</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+2.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="H5" t="n">
-        <v>75.02</v>
+        <v>1.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>167200</v>
+        <v>9010</v>
       </c>
       <c r="K5" t="n">
-        <v>159600</v>
+        <v>8810</v>
       </c>
       <c r="L5" t="n">
-        <v>175500</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>159200</v>
+        <v>8510</v>
       </c>
       <c r="N5" t="n">
-        <v>75</v>
+        <v>0.72</v>
       </c>
       <c r="O5" t="n">
-        <v>431282026800</v>
+        <v>122117162815</v>
       </c>
       <c r="P5" t="n">
-        <v>243500</v>
+        <v>9500</v>
       </c>
       <c r="Q5" t="n">
-        <v>71000</v>
+        <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>59000</v>
+        <v>-181000</v>
       </c>
       <c r="S5" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t>시장 전반의 불안감 속에서 로봇주에 대한 긍정적인 전망이 일부 있으나, 개인 투자자들의 혼란과 손실에 대한 우려가 혼재. 분석글 공개 후 급락 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['로봇주', '시장', '분석글']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14900</v>
+        <v>14940</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.15%</t>
+          <t>'+1.43%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="H6" t="n">
         <v>9.699999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>24868303940</v>
+        <v>25463484640</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 이슈와 연관된 부정적 언급 다수. 뱅크런 및 주가 조작 의혹 제기, 외인 보유율 관련 언급.</t>
+          <t>대우건설, 정치적 이슈와 맞물린 주가조작 의혹 제기. 일부 투자자들은 뱅크런 및 대차해지 중요성 강조.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['뱅크런', '주가조작', '이재명']</t>
+          <t>['주가조작', '뱅크런', '이재명']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217000</v>
+        <v>217250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.70%</t>
+          <t>'+0.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G7" t="n">
-        <v>1445</v>
+        <v>1495</v>
       </c>
       <c r="H7" t="n">
         <v>45.99</v>
@@ -1070,7 +1070,7 @@
         <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>1871957792250</v>
+        <v>1919093915500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명, 연기금 관련 정치적 언급과 더불어 주가 등락에 대한 다양한 기대와 우려가 혼재된 상황. 공매도 및 기관 매매 동향에 대한 언급이 있으나, 구체적인 근거는 부족.</t>
+          <t>삼성전자, 시장 전반의 정치적 이슈 및 연기금 매도세 속 혼조세. 일부 투자자들은 탈출 기회로 판단.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['연기금', '공매도', '매매동향']</t>
+          <t>['연기금', '이재명', '주가조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14910</v>
+        <v>14940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.27%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" t="n">
         <v>0.06</v>
@@ -1162,7 +1162,7 @@
         <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>26613768620</v>
+        <v>26729235000</v>
       </c>
       <c r="P8" t="n">
         <v>30800</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1258000</v>
+        <v>1262000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.10%</t>
+          <t>'-0.79%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="G9" t="n">
-        <v>1796</v>
+        <v>1902</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2492083719500</v>
+        <v>2551661135500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 상장 문제와 관련된 부정적인 의견이 지배적이며, 최태원 회장에 대한 비난과 경영 투명성 부족에 대한 지적이 다수. 안철수 의원의 발언이 언급.</t>
+          <t>SK하이닉스, 솔리다임 상장 이슈로 인한 중복상장 우려 및 경영진 사생활 문제로 주가 하락 압력. 투자자 불신 심화.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '최태원', '상장']</t>
+          <t>['솔리다임', '중복상장', '최태원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17850</v>
+        <v>17880</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.99%</t>
+          <t>'-2.83%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>28021727200</v>
+        <v>28795169980</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14390</v>
+        <v>14270</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.13%</t>
+          <t>'-4.93%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>36776921795</v>
+        <v>37458874365</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.31%</t>
+          <t>'-5.79%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F12" t="n">
         <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>10757366524</v>
+        <v>10927873552</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_12.xlsx
+++ b/data/trending_integrated_20261019_12.xlsx
@@ -571,20 +571,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+38.84%</t>
+          <t>'+29.96%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -595,28 +595,28 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1259</v>
+        <v>1345</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1432</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1748</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1386</v>
       </c>
       <c r="N2" t="n">
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20424000000</v>
+        <v>20450106940</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2970</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>890</v>
       </c>
       <c r="R2" t="n">
         <v>918000</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9470</v>
+        <v>9460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.07%</t>
+          <t>'+11.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
         <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>22226445530</v>
+        <v>22357672920</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>명신산업, 테슬라 로드스터 수혜주로 부각되며 전체 매출의 70% 테슬라 납품 사실에 주목. 11,000원 돌파 기대감.</t>
+          <t>테슬라 로드스터 수혜주로 언급되며 매출의 70%가 테슬라에 납품되는 점이 부각됨. 주가 상승에 대한 기대감이 있으나, 공매도, 프로그램 매도 등 부정적 요인과 혼재하며 약발이 3일이라는 언급도 있어 신중한 접근 필요.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '납품']</t>
+          <t>['테슬라', '로드스터', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -765,10 +765,10 @@
         <v>59</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G4" t="n">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>438544201850</v>
+        <v>444944051950</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -839,70 +839,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9190</v>
+        <v>14960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.00%</t>
+          <t>'+1.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F5" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>236</v>
+        <v>168</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9010</v>
+        <v>14730</v>
       </c>
       <c r="K5" t="n">
-        <v>8810</v>
+        <v>14500</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>15070</v>
       </c>
       <c r="M5" t="n">
-        <v>8510</v>
+        <v>14120</v>
       </c>
       <c r="N5" t="n">
-        <v>0.72</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>122117162815</v>
+        <v>26058212250</v>
       </c>
       <c r="P5" t="n">
-        <v>9500</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>-181000</v>
+        <v>32000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-29000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>시장 전반의 불안감 속에서 로봇주에 대한 긍정적인 전망이 일부 있으나, 개인 투자자들의 혼란과 손실에 대한 우려가 혼재. 분석글 공개 후 급락 가능성에 대한 언급.</t>
+          <t>이재명 대통령 관련 언급이 다수이며, 주가 조작 및 뱅크런에 대한 의혹 제기. 외인 보유율 조정 언급과 함께 대차 잔고에 대한 우려가 제기되나, 구체적인 팩트 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇주', '시장', '분석글']</t>
+          <t>['이재명', '뱅크런', '대차잔고']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14940</v>
+        <v>9090</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.43%</t>
+          <t>'+0.89%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.08</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>179</v>
+        <v>237</v>
       </c>
       <c r="H6" t="n">
-        <v>9.699999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14730</v>
+        <v>9010</v>
       </c>
       <c r="K6" t="n">
-        <v>14500</v>
+        <v>8810</v>
       </c>
       <c r="L6" t="n">
-        <v>15070</v>
+        <v>9500</v>
       </c>
       <c r="M6" t="n">
-        <v>14120</v>
+        <v>8510</v>
       </c>
       <c r="N6" t="n">
-        <v>9.779999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="O6" t="n">
-        <v>25463484640</v>
+        <v>124486087650</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>9500</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>2270</v>
       </c>
       <c r="R6" t="n">
-        <v>32000</v>
+        <v>-181000</v>
       </c>
       <c r="S6" t="n">
-        <v>-29000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 이슈와 맞물린 주가조작 의혹 제기. 일부 투자자들은 뱅크런 및 대차해지 중요성 강조.</t>
+          <t>시장 전반의 불안감 속에서 로봇주에 대한 긍정적인 전망이 일부 있으나, 개인 투자자들의 혼란과 손실에 대한 우려가 혼재. 분석글 공개 후 급락 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가조작', '뱅크런', '이재명']</t>
+          <t>['로봇주', '시장', '분석글']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217250</v>
+        <v>217000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.81%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G7" t="n">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="H7" t="n">
         <v>45.99</v>
@@ -1070,7 +1070,7 @@
         <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>1919093915500</v>
+        <v>1975268642000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자, 시장 전반의 정치적 이슈 및 연기금 매도세 속 혼조세. 일부 투자자들은 탈출 기회로 판단.</t>
+          <t>이재명 관련 언급과 함께 주가 변동 및 연기금, 외국인 매매 동향에 대한 다양한 의견이 혼재. 11월 반도체 수출 소식에 기반한 급등 예상도 있으나, 전반적으로 근거 없는 기대와 부정적 시각이 혼합됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['연기금', '이재명', '주가조작']</t>
+          <t>['연기금', '외국인', '반도체 수출']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14940</v>
+        <v>14950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
         <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H8" t="n">
         <v>0.06</v>
@@ -1162,7 +1162,7 @@
         <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>26729235000</v>
+        <v>26922958780</v>
       </c>
       <c r="P8" t="n">
         <v>30800</v>
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="G9" t="n">
-        <v>1902</v>
+        <v>1851</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1245,7 +1245,7 @@
         <v>1212000</v>
       </c>
       <c r="L9" t="n">
-        <v>1264000</v>
+        <v>1265000</v>
       </c>
       <c r="M9" t="n">
         <v>1208000</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2551661135500</v>
+        <v>2613853525000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 상장 이슈로 인한 중복상장 우려 및 경영진 사생활 문제로 주가 하락 압력. 투자자 불신 심화.</t>
+          <t>솔리다임 상장 관련 논란과 최태원 회장의 사생활 문제 등이 거론되며 부정적인 여론 형성. 중복 상장 우려 및 주가 하락 가능성에 대한 언급과 함께, 정치인 안철수 의원의 발언이 긍정적으로 인용됨.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17880</v>
+        <v>17950</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.83%</t>
+          <t>'-2.45%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1337,7 +1337,7 @@
         <v>17690</v>
       </c>
       <c r="L10" t="n">
-        <v>17950</v>
+        <v>17960</v>
       </c>
       <c r="M10" t="n">
         <v>17670</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>28795169980</v>
+        <v>29748244975</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1391,28 +1391,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14270</v>
+        <v>1209</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.93%</t>
+          <t>'-4.12%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15010</v>
+        <v>1261</v>
       </c>
       <c r="K11" t="n">
-        <v>14460</v>
+        <v>1301</v>
       </c>
       <c r="L11" t="n">
-        <v>15200</v>
+        <v>1339</v>
       </c>
       <c r="M11" t="n">
-        <v>13610</v>
+        <v>1145</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>37458874365</v>
+        <v>11009601014</v>
       </c>
       <c r="P11" t="n">
-        <v>28800</v>
+        <v>1950</v>
       </c>
       <c r="Q11" t="n">
-        <v>13610</v>
+        <v>192</v>
       </c>
       <c r="R11" t="n">
-        <v>35000</v>
+        <v>-321000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>멜콘, 과거 거래 이력 및 주포 활동 분석. 투자 주의 의견 제기.</t>
+          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '투자주의']</t>
+          <t>['데이터센터', 'AI', '성장성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,35 +1476,35 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>317240</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1188</v>
+        <v>14190</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.79%</t>
+          <t>'-5.46%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>64</v>
+      </c>
+      <c r="F12" t="n">
         <v>52</v>
       </c>
-      <c r="F12" t="n">
-        <v>20</v>
-      </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1261</v>
+        <v>15010</v>
       </c>
       <c r="K12" t="n">
-        <v>1301</v>
+        <v>14460</v>
       </c>
       <c r="L12" t="n">
-        <v>1339</v>
+        <v>15200</v>
       </c>
       <c r="M12" t="n">
-        <v>1145</v>
+        <v>13610</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>10927873552</v>
+        <v>38180946685</v>
       </c>
       <c r="P12" t="n">
-        <v>1950</v>
+        <v>28800</v>
       </c>
       <c r="Q12" t="n">
-        <v>192</v>
+        <v>13610</v>
       </c>
       <c r="R12" t="n">
-        <v>-321000</v>
+        <v>35000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
+          <t>멜콘, 과거 거래 이력 및 주포 활동 분석. 투자 주의 의견 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['데이터센터', 'AI', '성장성']</t>
+          <t>['주포', '거래량', '투자주의']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>317240</t>
+          <t>179880</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261019_12.xlsx
+++ b/data/trending_integrated_20261019_12.xlsx
@@ -584,7 +584,7 @@
         <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20450106940</v>
+        <v>20465882640</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대에 강관 950톤 공급 소식에 대한 기대감 고조. 외인 매집 확인, 전고점 돌파 전망.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 공급 단독 보도. 외인 매집 및 전고점 돌파 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9460</v>
+        <v>9450</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.95%</t>
+          <t>'+11.83%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G3" t="n">
         <v>207</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>22357672920</v>
+        <v>22510059965</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171000</v>
+        <v>171200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.27%</t>
+          <t>'+2.39%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>444944051950</v>
+        <v>454680692100</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14960</v>
+        <v>14950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.56%</t>
+          <t>'+1.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H5" t="n">
         <v>9.699999999999999</v>
@@ -886,7 +886,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>26058212250</v>
+        <v>26528155810</v>
       </c>
       <c r="P5" t="n">
         <v>40350</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9090</v>
+        <v>9110</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.89%</t>
+          <t>'+1.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F6" t="n">
         <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H6" t="n">
         <v>1.74</v>
@@ -978,7 +978,7 @@
         <v>0.72</v>
       </c>
       <c r="O6" t="n">
-        <v>124486087650</v>
+        <v>125946773230</v>
       </c>
       <c r="P6" t="n">
         <v>9500</v>
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="G7" t="n">
-        <v>1491</v>
+        <v>1534</v>
       </c>
       <c r="H7" t="n">
         <v>45.99</v>
@@ -1070,7 +1070,7 @@
         <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>1975268642000</v>
+        <v>1999547091750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명 관련 언급과 함께 주가 변동 및 연기금, 외국인 매매 동향에 대한 다양한 의견이 혼재. 11월 반도체 수출 소식에 기반한 급등 예상도 있으나, 전반적으로 근거 없는 기대와 부정적 시각이 혼합됨.</t>
+          <t>이재명, 연기금, 이주완 박사 등 다양한 정치적/인물 언급. 외인 매수세 유입 및 급등 기대와 매도 의견 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['연기금', '외국인', '반도체 수출']</t>
+          <t>['반도체', '외국인', '주가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14950</v>
+        <v>14900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.33%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1162,7 +1162,7 @@
         <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>26922958780</v>
+        <v>27040078620</v>
       </c>
       <c r="P8" t="n">
         <v>30800</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1262000</v>
+        <v>1259000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.79%</t>
+          <t>'-1.02%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="G9" t="n">
-        <v>1851</v>
+        <v>1772</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1245,7 +1245,7 @@
         <v>1212000</v>
       </c>
       <c r="L9" t="n">
-        <v>1265000</v>
+        <v>1266000</v>
       </c>
       <c r="M9" t="n">
         <v>1208000</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2613853525000</v>
+        <v>2664180329000</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 논란과 최태원 회장의 사생활 문제 등이 거론되며 부정적인 여론 형성. 중복 상장 우려 및 주가 하락 가능성에 대한 언급과 함께, 정치인 안철수 의원의 발언이 긍정적으로 인용됨.</t>
+          <t>솔리다임 중복 상장 우려로 인한 주가 하락세. 최태원 회장 및 안철수 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17950</v>
+        <v>17980</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.45%</t>
+          <t>'-2.28%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1337,7 +1337,7 @@
         <v>17690</v>
       </c>
       <c r="L10" t="n">
-        <v>17960</v>
+        <v>18000</v>
       </c>
       <c r="M10" t="n">
         <v>17670</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>29748244975</v>
+        <v>31069931030</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1391,28 +1391,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1209</v>
+        <v>14180</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-4.12%</t>
+          <t>'-5.53%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1261</v>
+        <v>15010</v>
       </c>
       <c r="K11" t="n">
-        <v>1301</v>
+        <v>14460</v>
       </c>
       <c r="L11" t="n">
-        <v>1339</v>
+        <v>15200</v>
       </c>
       <c r="M11" t="n">
-        <v>1145</v>
+        <v>13610</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>11009601014</v>
+        <v>38451691890</v>
       </c>
       <c r="P11" t="n">
-        <v>1950</v>
+        <v>28800</v>
       </c>
       <c r="Q11" t="n">
-        <v>192</v>
+        <v>13610</v>
       </c>
       <c r="R11" t="n">
-        <v>-321000</v>
+        <v>35000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
+          <t>멜콘, 과거 거래 이력 및 주포 활동 분석. 투자 주의 의견 제기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['데이터센터', 'AI', '성장성']</t>
+          <t>['주포', '거래량', '투자주의']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,35 +1476,35 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>317240</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14190</v>
+        <v>1189</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.46%</t>
+          <t>'-5.71%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>15010</v>
+        <v>1261</v>
       </c>
       <c r="K12" t="n">
-        <v>14460</v>
+        <v>1301</v>
       </c>
       <c r="L12" t="n">
-        <v>15200</v>
+        <v>1339</v>
       </c>
       <c r="M12" t="n">
-        <v>13610</v>
+        <v>1145</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>38180946685</v>
+        <v>11186884360</v>
       </c>
       <c r="P12" t="n">
-        <v>28800</v>
+        <v>1950</v>
       </c>
       <c r="Q12" t="n">
-        <v>13610</v>
+        <v>192</v>
       </c>
       <c r="R12" t="n">
-        <v>35000</v>
+        <v>-321000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>멜콘, 과거 거래 이력 및 주포 활동 분석. 투자 주의 의견 제기.</t>
+          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '투자주의']</t>
+          <t>['데이터센터', 'AI', '성장성']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>317240</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261019_12.xlsx
+++ b/data/trending_integrated_20261019_12.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F2" t="n">
         <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20465882640</v>
+        <v>20478545152</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9450</v>
+        <v>9460</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.83%</t>
+          <t>'+11.95%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" t="n">
         <v>61</v>
       </c>
       <c r="G3" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>22510059965</v>
+        <v>22715325425</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 수혜주로 언급되며 매출의 70%가 테슬라에 납품되는 점이 부각됨. 주가 상승에 대한 기대감이 있으나, 공매도, 프로그램 매도 등 부정적 요인과 혼재하며 약발이 3일이라는 언급도 있어 신중한 접근 필요.</t>
+          <t>테슬라 로드스터 관련 수혜주로 언급되며, 자사주 매입 호재가 있으나 공매도와 프로그램 매도에 대한 경계도 존재함.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '공매도']</t>
+          <t>['테슬라', '로드스터', '자사주 매입']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>171200</v>
+        <v>171100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+2.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>454680692100</v>
+        <v>460248981500</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14950</v>
+        <v>14960</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.49%</t>
+          <t>'+1.56%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F5" t="n">
         <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H5" t="n">
         <v>9.699999999999999</v>
@@ -886,7 +886,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>26528155810</v>
+        <v>26853469620</v>
       </c>
       <c r="P5" t="n">
         <v>40350</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이재명 대통령 관련 언급이 다수이며, 주가 조작 및 뱅크런에 대한 의혹 제기. 외인 보유율 조정 언급과 함께 대차 잔고에 대한 우려가 제기되나, 구체적인 팩트 기반 분석은 부족함.</t>
+          <t>이재명 관련 정치적 언급과 함께 대차 잔고 등 기술적인 언급이 있으나, 구체적인 실적이나 공시 기반의 분석은 부족함.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['이재명', '뱅크런', '대차잔고']</t>
+          <t>['대차 잔고', '뱅크런']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9110</v>
+        <v>9100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.11%</t>
+          <t>'+1.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F6" t="n">
         <v>57</v>
       </c>
       <c r="G6" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H6" t="n">
         <v>1.74</v>
@@ -978,7 +978,7 @@
         <v>0.72</v>
       </c>
       <c r="O6" t="n">
-        <v>125946773230</v>
+        <v>127526505175</v>
       </c>
       <c r="P6" t="n">
         <v>9500</v>
@@ -1044,7 +1044,7 @@
         <v>516</v>
       </c>
       <c r="G7" t="n">
-        <v>1534</v>
+        <v>1558</v>
       </c>
       <c r="H7" t="n">
         <v>45.99</v>
@@ -1070,7 +1070,7 @@
         <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>1999547091750</v>
+        <v>2047074005750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>이재명, 연기금, 이주완 박사 등 다양한 정치적/인물 언급. 외인 매수세 유입 및 급등 기대와 매도 의견 혼재.</t>
+          <t>이재명 관련 정치적 언급과 개인적인 시장 전망이 주를 이루며, 구체적인 사실 근거가 부족함.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', '외국인', '주가']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14900</v>
+        <v>14830</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.33%</t>
+          <t>'-0.80%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
         <v>35</v>
@@ -1162,7 +1162,7 @@
         <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>27040078620</v>
+        <v>27315084780</v>
       </c>
       <c r="P8" t="n">
         <v>30800</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1259000</v>
+        <v>1257000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.02%</t>
+          <t>'-1.18%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G9" t="n">
-        <v>1772</v>
+        <v>1724</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2664180329000</v>
+        <v>2713057610500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 중복 상장 우려로 인한 주가 하락세. 최태원 회장 및 안철수 관련 언급.</t>
+          <t>솔리다임 상장 관련 논란이 주된 내용이며, 정치인 발언과 주주들의 우려가 혼재되어 부정적인 sentiment를 보임.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복상장', '최태원']</t>
+          <t>['솔리다임', '상장', '금감원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17980</v>
+        <v>17970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.28%</t>
+          <t>'-2.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>31069931030</v>
+        <v>31518800345</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1391,28 +1391,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>TS트릴리온</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14180</v>
+        <v>1197</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.53%</t>
+          <t>'-5.08%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15010</v>
+        <v>1261</v>
       </c>
       <c r="K11" t="n">
-        <v>14460</v>
+        <v>1301</v>
       </c>
       <c r="L11" t="n">
-        <v>15200</v>
+        <v>1339</v>
       </c>
       <c r="M11" t="n">
-        <v>13610</v>
+        <v>1145</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>38451691890</v>
+        <v>11297594591</v>
       </c>
       <c r="P11" t="n">
-        <v>28800</v>
+        <v>1950</v>
       </c>
       <c r="Q11" t="n">
-        <v>13610</v>
+        <v>192</v>
       </c>
       <c r="R11" t="n">
-        <v>35000</v>
+        <v>-321000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>멜콘, 과거 거래 이력 및 주포 활동 분석. 투자 주의 의견 제기.</t>
+          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주포', '거래량', '투자주의']</t>
+          <t>['데이터센터', 'AI', '성장성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,35 +1476,35 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>317240</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TS트릴리온</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1189</v>
+        <v>14150</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-5.71%</t>
+          <t>'-5.73%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1261</v>
+        <v>15010</v>
       </c>
       <c r="K12" t="n">
-        <v>1301</v>
+        <v>14460</v>
       </c>
       <c r="L12" t="n">
-        <v>1339</v>
+        <v>15200</v>
       </c>
       <c r="M12" t="n">
-        <v>1145</v>
+        <v>13610</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>11186884360</v>
+        <v>38679656370</v>
       </c>
       <c r="P12" t="n">
-        <v>1950</v>
+        <v>28800</v>
       </c>
       <c r="Q12" t="n">
-        <v>192</v>
+        <v>13610</v>
       </c>
       <c r="R12" t="n">
-        <v>-321000</v>
+        <v>35000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>TS트릴리온, 데이터센터 건립 호재에도 불구하고 주가 부진. 동전주 탈출 기대.</t>
+          <t>멜콘, 과거 거래 이력 및 주포 활동 분석. 투자 주의 의견 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['데이터센터', 'AI', '성장성']</t>
+          <t>['주포', '거래량', '투자주의']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>317240</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
